--- a/Excel/01-CashFlow.xlsx
+++ b/Excel/01-CashFlow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_DA96859734F46AF68595C205E3A264B374596E66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A8B14BE-0869-47E1-B52F-641FB68613D1}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_326D66C0B83DBDC0E6A176517B92DFCB16052FFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6B279B-AF60-4F21-BE44-D82F0EB90B44}"/>
   <bookViews>
-    <workbookView xWindow="10224" yWindow="1236" windowWidth="12552" windowHeight="10272" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1044" windowWidth="12576" windowHeight="10776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCIB" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="192">
   <si>
     <t>TRANSACT</t>
   </si>
@@ -523,6 +523,12 @@
     <t>WHAIR-DIV</t>
   </si>
   <si>
+    <t>PTT-DIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTG </t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -614,6 +620,9 @@
   </si>
   <si>
     <t>SMART</t>
+  </si>
+  <si>
+    <t>Adj.</t>
   </si>
 </sst>
 </file>
@@ -643,43 +652,43 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Verdana"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -687,19 +696,19 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Verdana"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -729,7 +738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -767,6 +776,7 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1075,11 +1085,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H663"/>
+  <dimension ref="A1:I674"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="15" style="13" customWidth="1"/>
-    <col min="3" max="3" width="20.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.375" style="14" customWidth="1"/>
     <col min="4" max="4" width="16.375" style="15" customWidth="1"/>
     <col min="5" max="5" width="16" style="15" customWidth="1"/>
     <col min="6" max="6" width="16.375" style="14" customWidth="1"/>
@@ -14375,7 +14385,7 @@
         <v>6453</v>
       </c>
       <c r="F646" s="22">
-        <f t="shared" ref="F646:F658" si="112">F645-D646+E646</f>
+        <f t="shared" ref="F646:F673" si="112">F645-D646+E646</f>
         <v>109240.997192</v>
       </c>
       <c r="H646" s="33"/>
@@ -14425,26 +14435,25 @@
       <c r="G648" s="26"/>
     </row>
     <row r="649" spans="1:8" ht="15" customHeight="1">
-      <c r="A649" s="19">
-        <v>46295</v>
+      <c r="A649" s="19" t="s">
+        <v>6</v>
       </c>
       <c r="B649" s="19">
         <v>46297</v>
       </c>
-      <c r="C649" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="D649" s="31">
-        <v>46352.44</v>
-      </c>
-      <c r="E649" s="15">
+      <c r="C649" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D649" s="34">
+        <v>1319.67</v>
+      </c>
+      <c r="E649" s="21">
         <v>0</v>
       </c>
       <c r="F649" s="22">
         <f t="shared" si="112"/>
-        <v>210296.31719199999</v>
-      </c>
-      <c r="G649" s="26"/>
+        <v>255329.08719200001</v>
+      </c>
     </row>
     <row r="650" spans="1:8" ht="15" customHeight="1">
       <c r="A650" s="19">
@@ -14457,14 +14466,14 @@
         <v>130</v>
       </c>
       <c r="D650" s="31">
-        <v>22800.39</v>
+        <v>46352.44</v>
       </c>
       <c r="E650" s="15">
         <v>0</v>
       </c>
       <c r="F650" s="22">
         <f t="shared" si="112"/>
-        <v>187495.927192</v>
+        <v>208976.647192</v>
       </c>
       <c r="G650" s="26"/>
     </row>
@@ -14476,17 +14485,17 @@
         <v>46297</v>
       </c>
       <c r="C651" s="23" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D651" s="31">
-        <v>136051.82999999999</v>
+        <v>22800.39</v>
       </c>
       <c r="E651" s="15">
         <v>0</v>
       </c>
       <c r="F651" s="22">
         <f t="shared" si="112"/>
-        <v>51444.097192000001</v>
+        <v>186176.25719199999</v>
       </c>
       <c r="G651" s="26"/>
     </row>
@@ -14497,40 +14506,40 @@
       <c r="B652" s="19">
         <v>46297</v>
       </c>
-      <c r="C652" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D652" s="21">
-        <v>14.98</v>
-      </c>
-      <c r="E652" s="21">
+      <c r="C652" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D652" s="31">
+        <v>136051.82999999999</v>
+      </c>
+      <c r="E652" s="15">
         <v>0</v>
       </c>
       <c r="F652" s="22">
         <f t="shared" si="112"/>
-        <v>51429.117191999998</v>
+        <v>50124.427191999901</v>
       </c>
       <c r="G652" s="26"/>
     </row>
     <row r="653" spans="1:8" ht="15" customHeight="1">
       <c r="A653" s="19">
-        <v>46302</v>
+        <v>46295</v>
       </c>
       <c r="B653" s="19">
-        <v>46304</v>
-      </c>
-      <c r="C653" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D653" s="31">
-        <v>0</v>
-      </c>
-      <c r="E653" s="15">
-        <v>58370.42</v>
+        <v>46297</v>
+      </c>
+      <c r="C653" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D653" s="21">
+        <v>14.98</v>
+      </c>
+      <c r="E653" s="21">
+        <v>0</v>
       </c>
       <c r="F653" s="22">
         <f t="shared" si="112"/>
-        <v>109799.537192</v>
+        <v>50109.447191999898</v>
       </c>
       <c r="G653" s="26"/>
     </row>
@@ -14541,212 +14550,443 @@
       <c r="B654" s="19">
         <v>46304</v>
       </c>
-      <c r="C654" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D654" s="21">
-        <v>14.98</v>
-      </c>
-      <c r="E654" s="21">
-        <v>0</v>
+      <c r="C654" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D654" s="31">
+        <v>0</v>
+      </c>
+      <c r="E654" s="15">
+        <v>58370.42</v>
       </c>
       <c r="F654" s="22">
         <f t="shared" si="112"/>
-        <v>109784.55719199999</v>
+        <v>108479.86719200001</v>
       </c>
       <c r="G654" s="26"/>
     </row>
     <row r="655" spans="1:8" ht="15" customHeight="1">
+      <c r="A655" s="19">
+        <v>46302</v>
+      </c>
       <c r="B655" s="19">
-        <v>46307</v>
-      </c>
-      <c r="C655" s="14" t="s">
-        <v>143</v>
+        <v>46304</v>
+      </c>
+      <c r="C655" s="20" t="s">
+        <v>11</v>
       </c>
       <c r="D655" s="21">
-        <v>0</v>
+        <v>14.98</v>
       </c>
       <c r="E655" s="21">
-        <v>3780</v>
+        <v>0</v>
       </c>
       <c r="F655" s="22">
         <f t="shared" si="112"/>
-        <v>113564.55719199999</v>
-      </c>
-      <c r="H655" s="33"/>
+        <v>108464.88719199999</v>
+      </c>
+      <c r="G655" s="26"/>
     </row>
     <row r="656" spans="1:8" ht="15" customHeight="1">
-      <c r="A656" s="19">
-        <v>46307</v>
-      </c>
       <c r="B656" s="19">
-        <v>46310</v>
-      </c>
-      <c r="C656" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D656" s="31">
-        <v>21647.850000000002</v>
-      </c>
-      <c r="E656" s="15">
+        <v>46305</v>
+      </c>
+      <c r="C656" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D656" s="21">
+        <v>20</v>
+      </c>
+      <c r="E656" s="21">
         <v>0</v>
       </c>
       <c r="F656" s="22">
         <f t="shared" si="112"/>
-        <v>91916.707191999987</v>
-      </c>
-      <c r="G656" s="26"/>
-    </row>
-    <row r="657" spans="1:7" ht="15" customHeight="1">
-      <c r="A657" s="19">
+        <v>108444.88719199999</v>
+      </c>
+      <c r="H656" s="33"/>
+    </row>
+    <row r="657" spans="1:9" ht="15" customHeight="1">
+      <c r="B657" s="19">
         <v>46307</v>
       </c>
-      <c r="B657" s="19">
-        <v>46310</v>
-      </c>
-      <c r="C657" s="20" t="s">
-        <v>11</v>
+      <c r="C657" s="14" t="s">
+        <v>143</v>
       </c>
       <c r="D657" s="21">
-        <v>14.98</v>
+        <v>0</v>
       </c>
       <c r="E657" s="21">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="F657" s="22">
         <f t="shared" si="112"/>
-        <v>91901.727191999991</v>
-      </c>
-      <c r="G657" s="26"/>
-    </row>
-    <row r="658" spans="1:7" ht="15" customHeight="1">
+        <v>112224.88719199999</v>
+      </c>
+      <c r="H657" s="33"/>
+    </row>
+    <row r="658" spans="1:9" ht="15" customHeight="1">
       <c r="A658" s="19">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B658" s="19">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="C658" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D658" s="36">
-        <v>46603.390890000002</v>
+        <v>26</v>
+      </c>
+      <c r="D658" s="31">
+        <v>21647.85</v>
       </c>
       <c r="E658" s="15">
         <v>0</v>
       </c>
       <c r="F658" s="22">
         <f t="shared" si="112"/>
-        <v>45298.336301999989</v>
-      </c>
-    </row>
-    <row r="659" spans="1:7" ht="15" customHeight="1">
+        <v>90577.037192000003</v>
+      </c>
+      <c r="G658" s="26"/>
+    </row>
+    <row r="659" spans="1:9" ht="15" customHeight="1">
       <c r="A659" s="19">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B659" s="19">
-        <v>46314</v>
-      </c>
-      <c r="C659" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D659" s="36">
-        <v>34576.71</v>
-      </c>
-      <c r="E659" s="15">
+        <v>46310</v>
+      </c>
+      <c r="C659" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D659" s="21">
+        <v>14.98</v>
+      </c>
+      <c r="E659" s="21">
         <v>0</v>
       </c>
       <c r="F659" s="22">
-        <f t="shared" ref="F659:F662" si="113">F658-D659+E659</f>
-        <v>10721.62630199999</v>
-      </c>
-    </row>
-    <row r="660" spans="1:7" ht="15" customHeight="1">
-      <c r="A660" s="19">
-        <v>46309</v>
+        <f t="shared" si="112"/>
+        <v>90562.057191999993</v>
+      </c>
+      <c r="G659" s="26"/>
+    </row>
+    <row r="660" spans="1:9" ht="15" customHeight="1">
+      <c r="A660" s="19" t="s">
+        <v>6</v>
       </c>
       <c r="B660" s="19">
-        <v>46314</v>
-      </c>
-      <c r="C660" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D660" s="31">
-        <v>0</v>
-      </c>
-      <c r="E660" s="15">
-        <v>139938.16</v>
+        <v>46310</v>
+      </c>
+      <c r="C660" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D660" s="21">
+        <v>432</v>
+      </c>
+      <c r="E660" s="21">
+        <v>0</v>
       </c>
       <c r="F660" s="22">
-        <f t="shared" si="113"/>
-        <v>150659.78630199999</v>
-      </c>
-      <c r="G660" s="26"/>
-    </row>
-    <row r="661" spans="1:7" ht="15" customHeight="1">
+        <f t="shared" si="112"/>
+        <v>90130.057191999993</v>
+      </c>
+    </row>
+    <row r="661" spans="1:9" ht="15" customHeight="1">
       <c r="A661" s="19">
         <v>46309</v>
       </c>
       <c r="B661" s="19">
         <v>46314</v>
       </c>
-      <c r="C661" s="20" t="s">
+      <c r="C661" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D661" s="36">
+        <v>46603.390890000002</v>
+      </c>
+      <c r="E661" s="15">
+        <v>0</v>
+      </c>
+      <c r="F661" s="22">
+        <f t="shared" si="112"/>
+        <v>43526.666301999998</v>
+      </c>
+    </row>
+    <row r="662" spans="1:9" ht="15" customHeight="1">
+      <c r="A662" s="19">
+        <v>46309</v>
+      </c>
+      <c r="B662" s="19">
+        <v>46314</v>
+      </c>
+      <c r="C662" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D662" s="36">
+        <v>34576.71</v>
+      </c>
+      <c r="E662" s="15">
+        <v>0</v>
+      </c>
+      <c r="F662" s="22">
+        <f t="shared" si="112"/>
+        <v>8949.9563019999605</v>
+      </c>
+    </row>
+    <row r="663" spans="1:9" ht="15" customHeight="1">
+      <c r="A663" s="19">
+        <v>46309</v>
+      </c>
+      <c r="B663" s="19">
+        <v>46314</v>
+      </c>
+      <c r="C663" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D663" s="31">
+        <v>0</v>
+      </c>
+      <c r="E663" s="15">
+        <v>139940.04999999999</v>
+      </c>
+      <c r="F663" s="22">
+        <f t="shared" si="112"/>
+        <v>148890.00630199999</v>
+      </c>
+    </row>
+    <row r="664" spans="1:9" ht="15" customHeight="1">
+      <c r="A664" s="19">
+        <v>46309</v>
+      </c>
+      <c r="B664" s="19">
+        <v>46314</v>
+      </c>
+      <c r="C664" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D661" s="21">
+      <c r="D664" s="21">
         <v>14.98</v>
       </c>
-      <c r="E661" s="21">
-        <v>0</v>
-      </c>
-      <c r="F661" s="22">
-        <f t="shared" si="113"/>
-        <v>150644.80630199998</v>
-      </c>
-      <c r="G661" s="26"/>
-    </row>
-    <row r="662" spans="1:7" ht="15" customHeight="1">
-      <c r="A662" s="19">
+      <c r="E664" s="21">
+        <v>0</v>
+      </c>
+      <c r="F664" s="22">
+        <f t="shared" si="112"/>
+        <v>148875.02630200001</v>
+      </c>
+      <c r="G664" s="26"/>
+      <c r="H664" s="37"/>
+      <c r="I664" s="37"/>
+    </row>
+    <row r="665" spans="1:9" ht="15" customHeight="1">
+      <c r="A665" s="19">
         <v>46310</v>
       </c>
-      <c r="B662" s="19">
+      <c r="B665" s="19">
         <v>46315</v>
       </c>
-      <c r="C662" s="23" t="s">
+      <c r="C665" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D662" s="36">
+      <c r="D665" s="36">
         <v>56374.59</v>
       </c>
-      <c r="E662" s="15">
-        <v>0</v>
-      </c>
-      <c r="F662" s="22">
-        <f t="shared" si="113"/>
-        <v>94270.216301999986</v>
-      </c>
-    </row>
-    <row r="663" spans="1:7" ht="15" customHeight="1">
-      <c r="A663" s="19">
+      <c r="E665" s="15">
+        <v>0</v>
+      </c>
+      <c r="F665" s="22">
+        <f t="shared" si="112"/>
+        <v>92500.436302000002</v>
+      </c>
+    </row>
+    <row r="666" spans="1:9" ht="15" customHeight="1">
+      <c r="A666" s="19">
         <v>46310</v>
       </c>
-      <c r="B663" s="19">
+      <c r="B666" s="19">
         <v>46315</v>
       </c>
-      <c r="C663" s="20" t="s">
+      <c r="C666" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D663" s="21">
+      <c r="D666" s="21">
         <v>14.98</v>
       </c>
-      <c r="E663" s="21">
-        <v>0</v>
-      </c>
-      <c r="F663" s="22">
-        <f t="shared" ref="F663" si="114">F662-D663+E663</f>
-        <v>94255.23630199999</v>
-      </c>
-      <c r="G663" s="26"/>
+      <c r="E666" s="21">
+        <v>0</v>
+      </c>
+      <c r="F666" s="22">
+        <f t="shared" si="112"/>
+        <v>92485.456302000006</v>
+      </c>
+      <c r="G666" s="26"/>
+    </row>
+    <row r="667" spans="1:9" ht="15" customHeight="1">
+      <c r="B667" s="19">
+        <v>46315</v>
+      </c>
+      <c r="C667" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D667" s="21">
+        <v>30000</v>
+      </c>
+      <c r="E667" s="21">
+        <v>0</v>
+      </c>
+      <c r="F667" s="22">
+        <f t="shared" si="112"/>
+        <v>62485.456301999999</v>
+      </c>
+      <c r="H667" s="33"/>
+    </row>
+    <row r="668" spans="1:9" ht="15" customHeight="1">
+      <c r="A668" s="19">
+        <v>46314</v>
+      </c>
+      <c r="B668" s="19">
+        <v>46316</v>
+      </c>
+      <c r="C668" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D668" s="31">
+        <v>0</v>
+      </c>
+      <c r="E668" s="15">
+        <v>58370.42</v>
+      </c>
+      <c r="F668" s="22">
+        <f t="shared" si="112"/>
+        <v>120855.876302</v>
+      </c>
+    </row>
+    <row r="669" spans="1:9" ht="15" customHeight="1">
+      <c r="A669" s="19">
+        <v>46314</v>
+      </c>
+      <c r="B669" s="19">
+        <v>46316</v>
+      </c>
+      <c r="C669" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D669" s="21">
+        <v>14.98</v>
+      </c>
+      <c r="E669" s="21">
+        <v>0</v>
+      </c>
+      <c r="F669" s="22">
+        <f t="shared" si="112"/>
+        <v>120840.89630199999</v>
+      </c>
+      <c r="G669" s="26"/>
+      <c r="H669" s="37"/>
+      <c r="I669" s="37"/>
+    </row>
+    <row r="670" spans="1:9" ht="15" customHeight="1">
+      <c r="B670" s="19">
+        <v>46317</v>
+      </c>
+      <c r="C670" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D670" s="21">
+        <v>0</v>
+      </c>
+      <c r="E670" s="21">
+        <v>9450</v>
+      </c>
+      <c r="F670" s="22">
+        <f t="shared" si="112"/>
+        <v>130290.89630199999</v>
+      </c>
+      <c r="H670" s="33"/>
+    </row>
+    <row r="671" spans="1:9" ht="15" customHeight="1">
+      <c r="A671" s="19">
+        <v>46315</v>
+      </c>
+      <c r="B671" s="19">
+        <v>46317</v>
+      </c>
+      <c r="C671" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D671" s="36">
+        <v>21848.29</v>
+      </c>
+      <c r="E671" s="15">
+        <v>0</v>
+      </c>
+      <c r="F671" s="22">
+        <f t="shared" si="112"/>
+        <v>108442.606302</v>
+      </c>
+    </row>
+    <row r="672" spans="1:9" ht="15" customHeight="1">
+      <c r="A672" s="19">
+        <v>46315</v>
+      </c>
+      <c r="B672" s="19">
+        <v>46317</v>
+      </c>
+      <c r="C672" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="D672" s="36">
+        <v>18881.73</v>
+      </c>
+      <c r="E672" s="15">
+        <v>0</v>
+      </c>
+      <c r="F672" s="22">
+        <f t="shared" si="112"/>
+        <v>89560.876302000004</v>
+      </c>
+    </row>
+    <row r="673" spans="1:7" ht="15" customHeight="1">
+      <c r="A673" s="19">
+        <v>46315</v>
+      </c>
+      <c r="B673" s="19">
+        <v>46317</v>
+      </c>
+      <c r="C673" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D673" s="21">
+        <v>14.98</v>
+      </c>
+      <c r="E673" s="21">
+        <v>0</v>
+      </c>
+      <c r="F673" s="22">
+        <f t="shared" si="112"/>
+        <v>89545.896302000008</v>
+      </c>
+      <c r="G673" s="26"/>
+    </row>
+    <row r="674" spans="1:7" ht="15" customHeight="1">
+      <c r="A674" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B674" s="19">
+        <v>46323</v>
+      </c>
+      <c r="C674" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D674" s="21">
+        <v>0</v>
+      </c>
+      <c r="E674" s="21">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F674" s="22">
+        <f t="shared" ref="F674" si="113">F673-D674+E674</f>
+        <v>89547.046302000002</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14768,22 +15008,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -14791,7 +15031,7 @@
         <v>45597</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -14809,7 +15049,7 @@
         <v>45605</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3">
         <v>1613.93</v>
@@ -14830,7 +15070,7 @@
         <v>45605</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C4" s="3">
         <v>22118.67</v>
@@ -14851,7 +15091,7 @@
         <v>45607</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
@@ -14864,7 +15104,7 @@
         <v>119284.52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -14872,7 +15112,7 @@
         <v>45609</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C6" s="1">
         <v>330</v>
@@ -14885,7 +15125,7 @@
         <v>118954.52</v>
       </c>
       <c r="F6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -14893,7 +15133,7 @@
         <v>45614</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C7" s="1">
         <v>518</v>
@@ -14906,7 +15146,7 @@
         <v>118436.52</v>
       </c>
       <c r="F7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -14914,7 +15154,7 @@
         <v>45596</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -14946,22 +15186,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -14969,7 +15209,7 @@
         <v>45566</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -14987,7 +15227,7 @@
         <v>45566</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C3" s="1">
         <v>5000</v>
@@ -15000,7 +15240,7 @@
         <v>183426.47</v>
       </c>
       <c r="F3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15008,7 +15248,7 @@
         <v>45572</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C4" s="1">
         <v>639.86</v>
@@ -15021,7 +15261,7 @@
         <v>182786.61</v>
       </c>
       <c r="F4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15029,7 +15269,7 @@
         <v>45575</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="3">
         <v>2224.86</v>
@@ -15050,7 +15290,7 @@
         <v>45575</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3">
         <v>14381.63</v>
@@ -15071,7 +15311,7 @@
         <v>45576</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C7" s="3">
         <v>0</v>
@@ -15084,7 +15324,7 @@
         <v>167480.12</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15092,7 +15332,7 @@
         <v>45581</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C8" s="1">
         <v>245</v>
@@ -15105,7 +15345,7 @@
         <v>167235.12</v>
       </c>
       <c r="F8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15113,7 +15353,7 @@
         <v>45582</v>
       </c>
       <c r="B9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C9" s="1">
         <v>15000</v>
@@ -15126,7 +15366,7 @@
         <v>152235.12</v>
       </c>
       <c r="F9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15134,7 +15374,7 @@
         <v>45581</v>
       </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C10" s="1">
         <v>518</v>
@@ -15147,7 +15387,7 @@
         <v>151717.12</v>
       </c>
       <c r="F10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15155,7 +15395,7 @@
         <v>45596</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C11" s="3">
         <v>10000</v>
@@ -15168,7 +15408,7 @@
         <v>141717.12</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -15188,22 +15428,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15211,7 +15451,7 @@
         <v>45536</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -15229,7 +15469,7 @@
         <v>45538</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C3" s="1">
         <v>500</v>
@@ -15242,7 +15482,7 @@
         <v>100166.74</v>
       </c>
       <c r="F3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -15250,7 +15490,7 @@
         <v>45539</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C4" s="1">
         <v>100</v>
@@ -15263,7 +15503,7 @@
         <v>100066.74</v>
       </c>
       <c r="F4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15271,7 +15511,7 @@
         <v>45544</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="3">
         <v>393</v>
@@ -15292,7 +15532,7 @@
         <v>45544</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3">
         <v>27661.77</v>
@@ -15313,7 +15553,7 @@
         <v>45545</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C7" s="3">
         <v>901.06</v>
@@ -15326,7 +15566,7 @@
         <v>71110.91</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15334,7 +15574,7 @@
         <v>45545</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3">
         <v>40000</v>
@@ -15347,7 +15587,7 @@
         <v>31110.91</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15355,7 +15595,7 @@
         <v>45545</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -15368,7 +15608,7 @@
         <v>32410.91</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15376,7 +15616,7 @@
         <v>45546</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C10" s="1">
         <v>861.84</v>
@@ -15389,7 +15629,7 @@
         <v>31549.07</v>
       </c>
       <c r="F10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15397,7 +15637,7 @@
         <v>45546</v>
       </c>
       <c r="B11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C11" s="1">
         <v>3079.2</v>
@@ -15410,7 +15650,7 @@
         <v>28469.87</v>
       </c>
       <c r="F11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15418,7 +15658,7 @@
         <v>45547</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C12" s="3">
         <v>0</v>
@@ -15439,7 +15679,7 @@
         <v>45547</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C13" s="3">
         <v>0</v>
@@ -15460,7 +15700,7 @@
         <v>45565</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="3">
         <v>10000</v>
@@ -15473,7 +15713,7 @@
         <v>188426.47</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -15493,22 +15733,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15516,7 +15756,7 @@
         <v>45505</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -15534,7 +15774,7 @@
         <v>45513</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3">
         <v>1033.93</v>
@@ -15555,7 +15795,7 @@
         <v>45513</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C4" s="3">
         <v>32201.26</v>
@@ -15576,7 +15816,7 @@
         <v>45514</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C5" s="3">
         <v>943.86</v>
@@ -15589,7 +15829,7 @@
         <v>61289.74</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15597,7 +15837,7 @@
         <v>45514</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -15610,7 +15850,7 @@
         <v>101289.74</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15619,7 +15859,7 @@
         <v>45517</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C7" s="1">
         <v>60</v>
@@ -15632,7 +15872,7 @@
         <v>101229.74</v>
       </c>
       <c r="F7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -15640,7 +15880,7 @@
         <v>45522</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -15653,7 +15893,7 @@
         <v>102529.74</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15661,7 +15901,7 @@
         <v>45525</v>
       </c>
       <c r="B9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C9" s="1">
         <v>500</v>
@@ -15674,7 +15914,7 @@
         <v>102029.74</v>
       </c>
       <c r="F9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15682,7 +15922,7 @@
         <v>45531</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C10" s="3">
         <v>26363</v>
@@ -15695,7 +15935,7 @@
         <v>75666.740000000005</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15703,7 +15943,7 @@
         <v>45533</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C11" s="3">
         <v>0</v>
@@ -15716,7 +15956,7 @@
         <v>100666.74</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -15737,22 +15977,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15760,7 +16000,7 @@
         <v>45474</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -15778,7 +16018,7 @@
         <v>45480</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" s="3">
         <v>7200</v>
@@ -15799,7 +16039,7 @@
         <v>45480</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C4" s="3">
         <v>21390</v>
@@ -15812,7 +16052,7 @@
         <v>129069.9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -15820,7 +16060,7 @@
         <v>45481</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
@@ -15833,7 +16073,7 @@
         <v>133043.35999999999</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -15841,7 +16081,7 @@
         <v>45483</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3">
         <v>1674.86</v>
@@ -15854,7 +16094,7 @@
         <v>131368.5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -15862,7 +16102,7 @@
         <v>45483</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="3">
         <v>26681.71</v>
@@ -15883,7 +16123,7 @@
         <v>45483</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C8" s="3">
         <v>518</v>
@@ -15896,7 +16136,7 @@
         <v>104168.79</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15904,7 +16144,7 @@
         <v>45488</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -15917,7 +16157,7 @@
         <v>105468.79</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15925,7 +16165,7 @@
         <v>45504</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C10" s="3">
         <v>10000</v>
@@ -15938,7 +16178,7 @@
         <v>95468.79</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -15959,22 +16199,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -15982,7 +16222,7 @@
         <v>45444</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -16000,7 +16240,7 @@
         <v>45452</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3">
         <v>393</v>
@@ -16013,7 +16253,7 @@
         <v>30486.11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -16021,7 +16261,7 @@
         <v>45452</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C4" s="3">
         <v>13205.64</v>
@@ -16034,7 +16274,7 @@
         <v>17280.47</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -16042,7 +16282,7 @@
         <v>45453</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
@@ -16055,7 +16295,7 @@
         <v>20677.439999999999</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -16063,7 +16303,7 @@
         <v>45453</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C6" s="3">
         <v>7400</v>
@@ -16076,7 +16316,7 @@
         <v>13277.44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -16084,7 +16324,7 @@
         <v>45453</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C7" s="3">
         <v>3300</v>
@@ -16097,7 +16337,7 @@
         <v>9977.44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -16105,7 +16345,7 @@
         <v>45453</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -16118,7 +16358,7 @@
         <v>58977.440000000002</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -16126,7 +16366,7 @@
         <v>45454</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -16139,7 +16379,7 @@
         <v>240476.24</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -16147,7 +16387,7 @@
         <v>45454</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C10" s="3">
         <v>0</v>
@@ -16160,7 +16400,7 @@
         <v>280856.46000000002</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -16168,7 +16408,7 @@
         <v>45454</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C11" s="3">
         <v>0</v>
@@ -16181,7 +16421,7 @@
         <v>290856.46000000002</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -16189,7 +16429,7 @@
         <v>45455</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C12" s="3">
         <v>0</v>
@@ -16202,7 +16442,7 @@
         <v>293813.06</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -16210,7 +16450,7 @@
         <v>45455</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C13" s="3">
         <v>43000</v>
@@ -16223,7 +16463,7 @@
         <v>250813.06</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -16231,7 +16471,7 @@
         <v>45456</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C14" s="3">
         <v>0</v>
@@ -16252,7 +16492,7 @@
         <v>45456</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C15" s="3">
         <v>43000</v>
@@ -16265,7 +16505,7 @@
         <v>217813.06</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -16273,7 +16513,7 @@
         <v>45457</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C16" s="3">
         <v>49733.17</v>
@@ -16286,7 +16526,7 @@
         <v>168079.89</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -16294,7 +16534,7 @@
         <v>45458</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C17" s="3">
         <v>0</v>
@@ -16307,7 +16547,7 @@
         <v>169379.89</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -16315,7 +16555,7 @@
         <v>45461</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C18" s="3">
         <v>1115</v>
@@ -16328,7 +16568,7 @@
         <v>168264.89</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -16336,7 +16576,7 @@
         <v>45462</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C19" s="3">
         <v>518</v>
@@ -16349,7 +16589,7 @@
         <v>167746.89000000001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -16357,7 +16597,7 @@
         <v>45468</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C20" s="3">
         <v>0</v>
@@ -16370,7 +16610,7 @@
         <v>167851.9</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -16378,7 +16618,7 @@
         <v>45471</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C21" s="3">
         <v>192</v>
@@ -16391,7 +16631,7 @@
         <v>167659.9</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -16399,7 +16639,7 @@
         <v>45473</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C22" s="3">
         <v>10000</v>
@@ -16412,7 +16652,7 @@
         <v>157659.9</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -16436,22 +16676,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -16459,7 +16699,7 @@
         <v>45839</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -16478,7 +16718,7 @@
         <v>45848</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3">
         <v>1555.86</v>
@@ -16500,7 +16740,7 @@
         <v>45848</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C4" s="3">
         <v>8790.08</v>
@@ -16522,7 +16762,7 @@
         <v>45849</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
@@ -16535,7 +16775,7 @@
         <v>17907.509999999998</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -16543,7 +16783,7 @@
         <v>45851</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3">
         <v>60</v>
@@ -16556,7 +16796,7 @@
         <v>17847.509999999998</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G6" s="11"/>
     </row>
@@ -16565,7 +16805,7 @@
         <v>45859</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C7" s="3">
         <v>837.93</v>
@@ -16578,7 +16818,7 @@
         <v>17009.580000000002</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G7" s="11"/>
     </row>
@@ -16587,7 +16827,7 @@
         <v>45869</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3">
         <v>5000</v>
@@ -16600,7 +16840,7 @@
         <v>12009.58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -16608,7 +16848,7 @@
         <v>45869</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -16621,7 +16861,7 @@
         <v>50009.58</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -16659,22 +16899,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -16682,7 +16922,7 @@
         <v>45778</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -16701,7 +16941,7 @@
         <v>45787</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3">
         <v>914.93</v>
@@ -16723,7 +16963,7 @@
         <v>45787</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C4" s="3">
         <v>10319.040000000001</v>
@@ -16745,7 +16985,7 @@
         <v>45789</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C5" s="3">
         <v>192</v>
@@ -16758,7 +16998,7 @@
         <v>39936.31</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G5" s="11"/>
     </row>
@@ -16767,7 +17007,7 @@
         <v>45795</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3">
         <v>60</v>
@@ -16780,7 +17020,7 @@
         <v>39876.31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G6" s="11"/>
     </row>
@@ -16789,7 +17029,7 @@
         <v>45793</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C7" s="3">
         <v>0</v>
@@ -16802,7 +17042,7 @@
         <v>41176.31</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -16810,7 +17050,7 @@
         <v>45800</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C8" s="3">
         <v>837.93</v>
@@ -16823,7 +17063,7 @@
         <v>40338.379999999997</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G8" s="11"/>
     </row>
@@ -16832,7 +17072,7 @@
         <v>45800</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C9" s="3">
         <v>70</v>
@@ -16845,7 +17085,7 @@
         <v>40268.379999999997</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G9" s="11"/>
     </row>
@@ -16854,7 +17094,7 @@
         <v>45800</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C10" s="3">
         <v>1000</v>
@@ -16867,7 +17107,7 @@
         <v>39268.379999999997</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G10" s="11"/>
     </row>
@@ -16876,7 +17116,7 @@
         <v>45802</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C11" s="3">
         <v>245</v>
@@ -16889,7 +17129,7 @@
         <v>39023.379999999997</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G11" s="11"/>
     </row>
@@ -16898,7 +17138,7 @@
         <v>45807</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C12" s="3">
         <v>5000</v>
@@ -16911,7 +17151,7 @@
         <v>421825.39</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G12" s="11"/>
     </row>
@@ -16950,22 +17190,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -16973,7 +17213,7 @@
         <v>45778</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -16992,7 +17232,7 @@
         <v>45787</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3">
         <v>914.93</v>
@@ -17014,7 +17254,7 @@
         <v>45787</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C4" s="3">
         <v>10319.040000000001</v>
@@ -17036,7 +17276,7 @@
         <v>45789</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C5" s="3">
         <v>192</v>
@@ -17049,7 +17289,7 @@
         <v>39936.31</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G5" s="11"/>
     </row>
@@ -17058,7 +17298,7 @@
         <v>45795</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3">
         <v>60</v>
@@ -17071,7 +17311,7 @@
         <v>39876.31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G6" s="11"/>
     </row>
@@ -17080,7 +17320,7 @@
         <v>45793</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C7" s="3">
         <v>0</v>
@@ -17093,7 +17333,7 @@
         <v>41176.31</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -17101,7 +17341,7 @@
         <v>45800</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C8" s="3">
         <v>837.93</v>
@@ -17114,7 +17354,7 @@
         <v>40338.379999999997</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G8" s="11"/>
     </row>
@@ -17123,7 +17363,7 @@
         <v>45800</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C9" s="3">
         <v>70</v>
@@ -17136,7 +17376,7 @@
         <v>40268.379999999997</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G9" s="11"/>
     </row>
@@ -17145,7 +17385,7 @@
         <v>45800</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C10" s="3">
         <v>1000</v>
@@ -17158,7 +17398,7 @@
         <v>39268.379999999997</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G10" s="11"/>
     </row>
@@ -17167,7 +17407,7 @@
         <v>45802</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C11" s="3">
         <v>245</v>
@@ -17180,7 +17420,7 @@
         <v>39023.379999999997</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G11" s="11"/>
     </row>
@@ -17189,7 +17429,7 @@
         <v>45807</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C12" s="3">
         <v>5000</v>
@@ -17202,7 +17442,7 @@
         <v>421825.39</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G12" s="11"/>
     </row>
@@ -17241,22 +17481,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -17264,7 +17504,7 @@
         <v>45748</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -17282,7 +17522,7 @@
         <v>45748</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" s="3">
         <v>27000</v>
@@ -17295,7 +17535,7 @@
         <v>29455.759999999998</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -17303,7 +17543,7 @@
         <v>45748</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3">
         <v>0</v>
@@ -17316,7 +17556,7 @@
         <v>60455.76</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -17324,7 +17564,7 @@
         <v>45752</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C5" s="3">
         <v>60</v>
@@ -17337,7 +17577,7 @@
         <v>60395.76</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -17345,7 +17585,7 @@
         <v>45755</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -17358,7 +17598,7 @@
         <v>61294.81</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -17366,7 +17606,7 @@
         <v>45756</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="3">
         <v>914.93</v>
@@ -17387,7 +17627,7 @@
         <v>45756</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3">
         <v>4476.8100000000004</v>
@@ -17408,7 +17648,7 @@
         <v>45757</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C9" s="3">
         <v>660.79</v>
@@ -17421,7 +17661,7 @@
         <v>55242.28</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -17429,7 +17669,7 @@
         <v>45761</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C10" s="3">
         <v>0</v>
@@ -17442,7 +17682,7 @@
         <v>56542.28</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -17450,7 +17690,7 @@
         <v>45765</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C11" s="3">
         <v>60</v>
@@ -17463,7 +17703,7 @@
         <v>56482.28</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -17471,7 +17711,7 @@
         <v>45770</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C12" s="3">
         <v>60</v>
@@ -17484,7 +17724,7 @@
         <v>56422.28</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -17492,7 +17732,7 @@
         <v>45772</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C13" s="3">
         <v>60</v>
@@ -17505,7 +17745,7 @@
         <v>56362.28</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -17513,7 +17753,7 @@
         <v>45777</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="3">
         <v>5000</v>
@@ -17526,7 +17766,7 @@
         <v>51362.28</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -17564,22 +17804,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -17587,7 +17827,7 @@
         <v>45717</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -17599,7 +17839,7 @@
         <v>32906.370000000003</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -17607,7 +17847,7 @@
         <v>45727</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C3" s="3">
         <v>0</v>
@@ -17620,7 +17860,7 @@
         <v>80006.37</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -17628,7 +17868,7 @@
         <v>45728</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C4" s="3">
         <v>1576.53</v>
@@ -17649,7 +17889,7 @@
         <v>45728</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="3">
         <v>12586.08</v>
@@ -17670,7 +17910,7 @@
         <v>45731</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -17683,7 +17923,7 @@
         <v>67143.759999999995</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -17691,7 +17931,7 @@
         <v>45735</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C7" s="3">
         <v>518</v>
@@ -17704,7 +17944,7 @@
         <v>66625.759999999995</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -17712,7 +17952,7 @@
         <v>45739</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C8" s="3">
         <v>60</v>
@@ -17725,7 +17965,7 @@
         <v>66565.759999999995</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -17733,7 +17973,7 @@
         <v>45741</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C9" s="3">
         <v>50</v>
@@ -17746,7 +17986,7 @@
         <v>66515.759999999995</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -17754,7 +17994,7 @@
         <v>45747</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C10" s="3">
         <v>10000</v>
@@ -17775,7 +18015,7 @@
         <v>45747</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C11" s="3">
         <v>60</v>
@@ -17788,7 +18028,7 @@
         <v>56455.76</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -17826,22 +18066,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -17849,7 +18089,7 @@
         <v>45689</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -17867,7 +18107,7 @@
         <v>45693</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" s="3">
         <v>300</v>
@@ -17888,7 +18128,7 @@
         <v>45695</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C4" s="3">
         <v>817</v>
@@ -17901,7 +18141,7 @@
         <v>51178.57</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -17909,7 +18149,7 @@
         <v>45697</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="3">
         <v>973</v>
@@ -17930,7 +18170,7 @@
         <v>45697</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3">
         <v>25099.599999999999</v>
@@ -17951,7 +18191,7 @@
         <v>45702</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C7" s="3">
         <v>0</v>
@@ -17975,7 +18215,7 @@
         <v>45703</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -17999,7 +18239,7 @@
         <v>45706</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C9" s="3">
         <v>13322.8</v>
@@ -18020,7 +18260,7 @@
         <v>45706</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C10" s="3">
         <v>13322.8</v>
@@ -18041,7 +18281,7 @@
         <v>45707</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C11" s="3">
         <v>0</v>
@@ -18065,7 +18305,7 @@
         <v>45709</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C12" s="3">
         <v>518</v>
@@ -18078,7 +18318,7 @@
         <v>49242.37</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -18086,7 +18326,7 @@
         <v>45714</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C13" s="3">
         <v>6336</v>
@@ -18107,7 +18347,7 @@
         <v>45716</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="3">
         <v>10000</v>
@@ -18157,22 +18397,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -18180,7 +18420,7 @@
         <v>45658</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -18198,7 +18438,7 @@
         <v>45658</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" s="3">
         <v>48092</v>
@@ -18219,7 +18459,7 @@
         <v>45839</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C4" s="3">
         <v>497</v>
@@ -18232,7 +18472,7 @@
         <v>42929.59</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -18240,7 +18480,7 @@
         <v>45870</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
@@ -18253,7 +18493,7 @@
         <v>46946.720000000001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -18261,7 +18501,7 @@
         <v>45665</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3">
         <v>1900</v>
@@ -18274,7 +18514,7 @@
         <v>45046.720000000001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -18282,7 +18522,7 @@
         <v>45666</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="3">
         <v>1613.93</v>
@@ -18303,7 +18543,7 @@
         <v>45666</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3">
         <v>22915.82</v>
@@ -18324,7 +18564,7 @@
         <v>45667</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C9" s="3">
         <v>4017.13</v>
@@ -18337,7 +18577,7 @@
         <v>16499.84</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -18345,7 +18585,7 @@
         <v>45667</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C10" s="3">
         <v>0</v>
@@ -18358,7 +18598,7 @@
         <v>65999.839999999997</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -18366,7 +18606,7 @@
         <v>45668</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C11" s="3">
         <v>904.27</v>
@@ -18379,7 +18619,7 @@
         <v>65095.57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -18387,7 +18627,7 @@
         <v>45671</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C12" s="3">
         <v>4100</v>
@@ -18408,7 +18648,7 @@
         <v>45672</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C13" s="3">
         <v>0</v>
@@ -18421,7 +18661,7 @@
         <v>62295.57</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -18429,7 +18669,7 @@
         <v>45684</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C14" s="3">
         <v>0</v>
@@ -18442,7 +18682,7 @@
         <v>72295.570000000007</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -18450,7 +18690,7 @@
         <v>45685</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C15" s="3">
         <v>5000</v>
@@ -18463,7 +18703,7 @@
         <v>67295.570000000007</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -18471,7 +18711,7 @@
         <v>45685</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C16" s="3">
         <v>5000</v>
@@ -18484,7 +18724,7 @@
         <v>62295.57</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -18492,7 +18732,7 @@
         <v>45688</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C17" s="3">
         <v>10000</v>
@@ -18505,7 +18745,7 @@
         <v>52295.57</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -18541,22 +18781,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -18564,7 +18804,7 @@
         <v>45992</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -18582,7 +18822,7 @@
         <v>45997</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C3" s="3">
         <v>192</v>
@@ -18595,7 +18835,7 @@
         <v>118726.17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -18603,7 +18843,7 @@
         <v>46000</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3">
         <v>0</v>
@@ -18616,7 +18856,7 @@
         <v>121726.17</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -18624,7 +18864,7 @@
         <v>46001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="3">
         <v>1613.93</v>
@@ -18645,7 +18885,7 @@
         <v>46001</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3">
         <v>19175.650000000001</v>
@@ -18666,7 +18906,7 @@
         <v>46005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C7" s="3">
         <v>660.79</v>
@@ -18679,7 +18919,7 @@
         <v>100275.8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -18687,7 +18927,7 @@
         <v>46006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -18700,7 +18940,7 @@
         <v>101575.8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -18708,7 +18948,7 @@
         <v>46016</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -18721,7 +18961,7 @@
         <v>101818.59</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -18729,7 +18969,7 @@
         <v>46022</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C10" s="1">
         <v>300</v>
@@ -18742,7 +18982,7 @@
         <v>101518.59</v>
       </c>
       <c r="F10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -18750,7 +18990,7 @@
         <v>45596</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C11" s="3">
         <v>10000</v>
@@ -18763,7 +19003,7 @@
         <v>91518.59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
